--- a/Piaui/2026/Julho/ResultadosTRI_3EM_LP/Simulado_III/DistriAlunosClasseLP3serie_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_LP/Simulado_III/DistriAlunosClasseLP3serie_S3.xlsx
@@ -429,10 +429,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C4" t="n">
-        <v>2.772</v>
+        <v>2.762</v>
       </c>
     </row>
     <row r="5">
@@ -440,10 +440,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>1696</v>
       </c>
       <c r="C5" t="n">
-        <v>5.719</v>
+        <v>5.699</v>
       </c>
     </row>
     <row r="6">
@@ -451,10 +451,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="C6" t="n">
-        <v>8.021</v>
+        <v>8.031</v>
       </c>
     </row>
     <row r="7">
@@ -462,10 +462,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>2537</v>
+        <v>2546</v>
       </c>
       <c r="C7" t="n">
-        <v>8.525</v>
+        <v>8.555</v>
       </c>
     </row>
     <row r="8">
@@ -473,10 +473,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>2555</v>
+        <v>2539</v>
       </c>
       <c r="C8" t="n">
-        <v>8.585</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="9">
@@ -484,10 +484,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>2796</v>
+        <v>2811</v>
       </c>
       <c r="C9" t="n">
-        <v>9.395</v>
+        <v>9.446</v>
       </c>
     </row>
     <row r="10">
@@ -495,10 +495,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="C10" t="n">
-        <v>11.112</v>
+        <v>11.109</v>
       </c>
     </row>
     <row r="11">
@@ -506,10 +506,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>3716</v>
+        <v>3713</v>
       </c>
       <c r="C11" t="n">
-        <v>12.487</v>
+        <v>12.476</v>
       </c>
     </row>
     <row r="12">
@@ -517,10 +517,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>3470</v>
+        <v>3490</v>
       </c>
       <c r="C12" t="n">
-        <v>11.66</v>
+        <v>11.727</v>
       </c>
     </row>
     <row r="13">
@@ -528,10 +528,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>2771</v>
+        <v>2755</v>
       </c>
       <c r="C13" t="n">
-        <v>9.311</v>
+        <v>9.257</v>
       </c>
     </row>
     <row r="14">
@@ -539,10 +539,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>2101</v>
+        <v>2126</v>
       </c>
       <c r="C14" t="n">
-        <v>7.06</v>
+        <v>7.144</v>
       </c>
     </row>
     <row r="15">
@@ -550,10 +550,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>1593</v>
+        <v>1566</v>
       </c>
       <c r="C15" t="n">
-        <v>5.353</v>
+        <v>5.262</v>
       </c>
     </row>
   </sheetData>
